--- a/isSent/HR_Email_List_05.xlsx
+++ b/isSent/HR_Email_List_05.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SURAJ\Resume\EmailAutomation\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SURAJ\Resume\EmailAutomation\isSent\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
   <si>
     <t>Email ID</t>
   </si>
@@ -175,6 +175,117 @@
   </si>
   <si>
     <t>people@mindtree.com</t>
+  </si>
+  <si>
+    <t>sheela.venkatesh@sap.com</t>
+  </si>
+  <si>
+    <t>vijay.venkatraman@sap.com</t>
+  </si>
+  <si>
+    <t>sunitha.rm@sap.com</t>
+  </si>
+  <si>
+    <t>recruitment.chennai@nokia.com</t>
+  </si>
+  <si>
+    <t>blr.freshers@nokia.com</t>
+  </si>
+  <si>
+    <t>career_blr@nokia.com</t>
+  </si>
+  <si>
+    <t>wpcareers@nokia.com</t>
+  </si>
+  <si>
+    <t>tejal_chauhan@dell.com</t>
+  </si>
+  <si>
+    <t>vivek_agarwal@dell.com</t>
+  </si>
+  <si>
+    <t>lingesh_kumar@dell.com</t>
+  </si>
+  <si>
+    <t>sai_prashanth@dell.com</t>
+  </si>
+  <si>
+    <t>carrers_india@dell.com</t>
+  </si>
+  <si>
+    <t>raksha.nm@siemens.com</t>
+  </si>
+  <si>
+    <t>shapethefuture.in@siemens.com</t>
+  </si>
+  <si>
+    <t>resumes.bangalore@siemens.com</t>
+  </si>
+  <si>
+    <t>careersblr.in@siemens.com</t>
+  </si>
+  <si>
+    <t>careers.scs@siemens.com</t>
+  </si>
+  <si>
+    <t>career.scs@siemens.com</t>
+  </si>
+  <si>
+    <t>lucky.jindal@honeywell.com</t>
+  </si>
+  <si>
+    <t>sreedevi.basa@honeywell.com</t>
+  </si>
+  <si>
+    <t>seema.bansal@honeywell.com</t>
+  </si>
+  <si>
+    <t>nameeta.kagva@honeywell.com</t>
+  </si>
+  <si>
+    <t>vineet.haritha@honeywell.com</t>
+  </si>
+  <si>
+    <t>amashok@cisco.com</t>
+  </si>
+  <si>
+    <t>ppundir@cisco.com</t>
+  </si>
+  <si>
+    <t>india-jobs@cisco.com</t>
+  </si>
+  <si>
+    <t>apply-here@cisco.com</t>
+  </si>
+  <si>
+    <t>rajendra.p.prasad@oracle.com</t>
+  </si>
+  <si>
+    <t>savita.hortikar@oracle.com</t>
+  </si>
+  <si>
+    <t>nanditha.sudhindra@oracle.com</t>
+  </si>
+  <si>
+    <t>smitha.shanbag@oracle.com</t>
+  </si>
+  <si>
+    <t>harish.muniraju@oracle.com</t>
+  </si>
+  <si>
+    <t>campusrelations_in@oracle.com</t>
+  </si>
+  <si>
+    <t>laxmi.anand@oracle.com</t>
+  </si>
+  <si>
+    <t>siva.machiraju@oracle.com</t>
+  </si>
+  <si>
+    <t>madhushree_manjunath@mindtree.com</t>
+  </si>
+  <si>
+    <t>imaginedoenjoy@mindtree.com</t>
   </si>
 </sst>
 </file>
@@ -514,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.6328125" bestFit="1" customWidth="1"/>
@@ -780,6 +891,196 @@
         <v>51</v>
       </c>
     </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
